--- a/www/download/IND.abstract_labour.emp.s.mv.rpPE.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48668.626</t>
+          <t>48668626367.2355</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48704.123</t>
+          <t>48704122616.3629</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50265.152</t>
+          <t>50265152232.277</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54842.025</t>
+          <t>54842025421.9938</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57925.672</t>
+          <t>57925671731.6153</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>62717.968</t>
+          <t>62717967539.2776</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63590.52</t>
+          <t>63590520411.937</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>65811.229</t>
+          <t>65811228621.8257</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>62076.326</t>
+          <t>62076325584.0698</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>66376.126</t>
+          <t>66376126160.7884</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>66832.124</t>
+          <t>66832124207.1219</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>66639.237</t>
+          <t>66639236945.3067</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>64149.252</t>
+          <t>64149252038.5666</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>66133.135</t>
+          <t>66133134863.0913</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>70012.727</t>
+          <t>70012727075.0195</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23204.81</t>
+          <t>23204810031.6732</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23230.835</t>
+          <t>23230835294.3066</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23922.777</t>
+          <t>23922776667.4241</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25619.811</t>
+          <t>25619811236.537</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26882.464</t>
+          <t>26882464332.0147</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28512.854</t>
+          <t>28512853535.2239</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>29047.486</t>
+          <t>29047485607.5456</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28710.868</t>
+          <t>28710868260.0358</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26130.169</t>
+          <t>26130168700.2992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>29081.047</t>
+          <t>29081046688.3786</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>28281.396</t>
+          <t>28281395712.3268</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>27483.552</t>
+          <t>27483552000.7229</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>25983.016</t>
+          <t>25983015885.5293</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>25447.307</t>
+          <t>25447306684.8006</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>24682.817</t>
+          <t>24682816583.339</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19428.551</t>
+          <t>19428551004.3927</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19444.084</t>
+          <t>19444083943.3588</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20099.862</t>
+          <t>20099862285.7376</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21718.861</t>
+          <t>21718860935.8538</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22791.86</t>
+          <t>22791859616.7503</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24775.423</t>
+          <t>24775422637.3646</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25396.989</t>
+          <t>25396988650.82</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25040.125</t>
+          <t>25040125305.0361</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22926.534</t>
+          <t>22926534452.7461</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24963.892</t>
+          <t>24963891693.2278</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>24865.597</t>
+          <t>24865596822.2651</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>24788.954</t>
+          <t>24788953625.5495</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>23673.183</t>
+          <t>23673182741.6368</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>23863.412</t>
+          <t>23863411580.7672</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>24005.479</t>
+          <t>24005479279.7661</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12966.215</t>
+          <t>12966214606.2824</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13245.031</t>
+          <t>13245030694.9313</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12477.233</t>
+          <t>12477233347.0571</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11719.647</t>
+          <t>11719646971.8602</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11823.522</t>
+          <t>11823522404.2587</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11562.311</t>
+          <t>11562311034.1371</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11600.115</t>
+          <t>11600114568.7241</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11491.33</t>
+          <t>11491329941.0277</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11588.351</t>
+          <t>11588350547.1828</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13073.456</t>
+          <t>13073456104.3827</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>13305.902</t>
+          <t>13305902055.529</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13692.199</t>
+          <t>13692199371.711</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>13647.516</t>
+          <t>13647515562.9462</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>13818.933</t>
+          <t>13818933303.6593</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>14110.524</t>
+          <t>14110523624.7176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>380886.432</t>
+          <t>380886431533.993</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>375127.183</t>
+          <t>375127183093.491</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>392863.303</t>
+          <t>392863303281.171</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>416594.814</t>
+          <t>416594814437.259</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>446916.942</t>
+          <t>446916941513.779</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>489437.86</t>
+          <t>489437859551.726</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>504606.835</t>
+          <t>504606835405.473</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>523455.044</t>
+          <t>523455043778.179</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>499785.682</t>
+          <t>499785681878.839</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>552564.466</t>
+          <t>552564465912.223</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>563654.866</t>
+          <t>563654865635.646</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>585754.534</t>
+          <t>585754533642.387</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>582530.726</t>
+          <t>582530725852.888</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>581792.914</t>
+          <t>581792913785.254</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>604083.587</t>
+          <t>604083587456.372</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>112142.185</t>
+          <t>112142184827.315</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>112109.735</t>
+          <t>112109734764.672</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>114820.256</t>
+          <t>114820256023.484</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124473.349</t>
+          <t>124473348759.21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>130644.984</t>
+          <t>130644983650.574</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>139849.041</t>
+          <t>139849040890.208</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>141281.964</t>
+          <t>141281964222.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>140284.217</t>
+          <t>140284217265.179</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>129451.797</t>
+          <t>129451796712.153</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>140094.031</t>
+          <t>140094031475.137</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>139188.174</t>
+          <t>139188173860.895</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>138306.149</t>
+          <t>138306148792.418</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>132595.686</t>
+          <t>132595686474.565</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>128621.15</t>
+          <t>128621149940.222</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>123918.796</t>
+          <t>123918796164.259</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2479975.649</t>
+          <t>2479975648976.18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2527793.072</t>
+          <t>2527793071657.34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2591756.926</t>
+          <t>2591756925891.53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2707727.155</t>
+          <t>2707727154731.71</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2772274.55</t>
+          <t>2772274549741.68</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2949331.944</t>
+          <t>2949331943633.28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3229788.13</t>
+          <t>3229788130096.61</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3391752.521</t>
+          <t>3391752520798.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3286827.028</t>
+          <t>3286827027828.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3516307.035</t>
+          <t>3516307034978.66</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3568259.536</t>
+          <t>3568259535668.21</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3507974.116</t>
+          <t>3507974115860.43</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3374854.387</t>
+          <t>3374854387331.55</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3393358.704</t>
+          <t>3393358704103.69</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3472630.257</t>
+          <t>3472630256799.35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2527.878</t>
+          <t>2527877714.48903</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2532.762</t>
+          <t>2532761931.56296</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2500.39</t>
+          <t>2500390406.00606</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2584.313</t>
+          <t>2584313293.44543</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2724.939</t>
+          <t>2724938995.28021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2939.244</t>
+          <t>2939243585.06821</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3091.703</t>
+          <t>3091703440.77829</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3118.961</t>
+          <t>3118961336.08756</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2910.489</t>
+          <t>2910488611.39803</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3096.281</t>
+          <t>3096281280.00308</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3080.931</t>
+          <t>3080931278.59047</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3135.15</t>
+          <t>3135150451.41462</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>3134.917</t>
+          <t>3134916930.77745</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3091.074</t>
+          <t>3091073516.42186</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3082.643</t>
+          <t>3082642951.65963</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42782.176</t>
+          <t>42782176114.8401</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42074.401</t>
+          <t>42074400928.099</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42384.89</t>
+          <t>42384889824.4619</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43988.543</t>
+          <t>43988542538.4646</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44444.264</t>
+          <t>44444264178.7861</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>46335.768</t>
+          <t>46335768046.4367</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>44652.797</t>
+          <t>44652797334.6248</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43888.218</t>
+          <t>43888217836.3154</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39448.586</t>
+          <t>39448586084.2748</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>42303.657</t>
+          <t>42303656835.7806</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>42343.491</t>
+          <t>42343491184.4314</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>41999.783</t>
+          <t>41999782691.6997</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40046.593</t>
+          <t>40046593256.026</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39592.828</t>
+          <t>39592827835.9758</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39098.812</t>
+          <t>39098812367.9339</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>262042.61</t>
+          <t>262042609933.217</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>252342.525</t>
+          <t>252342524503.318</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>251373.046</t>
+          <t>251373045718.889</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>274520.294</t>
+          <t>274520293563.927</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>280801.383</t>
+          <t>280801383282.019</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>291769.548</t>
+          <t>291769547798.325</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>291170.03</t>
+          <t>291170030177.791</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>284268.885</t>
+          <t>284268885452.002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>260009.932</t>
+          <t>260009931557.016</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>278833.697</t>
+          <t>278833696724.969</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>265805.447</t>
+          <t>265805447141.93</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>256616.465</t>
+          <t>256616464982.642</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>244018.587</t>
+          <t>244018586567.757</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>237671.64</t>
+          <t>237671640455.395</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>239257.235</t>
+          <t>239257234596.579</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17622.804</t>
+          <t>17622803832.0458</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17592.201</t>
+          <t>17592201496.6227</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18428.657</t>
+          <t>18428657274.2709</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20098.899</t>
+          <t>20098899084.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21102.844</t>
+          <t>21102843960.1437</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22392.454</t>
+          <t>22392453880.6071</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22841.9</t>
+          <t>22841899987.3726</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22684.761</t>
+          <t>22684761167.7719</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20667.472</t>
+          <t>20667472270.824</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>21702.299</t>
+          <t>21702299149.0829</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>21549.431</t>
+          <t>21549430982.8439</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21667.974</t>
+          <t>21667973609.6604</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>19299.865</t>
+          <t>19299865407.9618</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>19212.641</t>
+          <t>19212640977.2977</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>18544.477</t>
+          <t>18544476980.2619</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>76246.64</t>
+          <t>76246640390.2482</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>80463.715</t>
+          <t>80463715101.0775</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>85607.809</t>
+          <t>85607808951.7309</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>96904.102</t>
+          <t>96904102409.031</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>106143.708</t>
+          <t>106143707604.145</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>119759.706</t>
+          <t>119759705721.317</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>126252.224</t>
+          <t>126252223972.395</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>128603.192</t>
+          <t>128603191946.651</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>121304.424</t>
+          <t>121304423550.085</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>132612.392</t>
+          <t>132612392257.693</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>137480.816</t>
+          <t>137480815959.273</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>139109.738</t>
+          <t>139109737745.827</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>133976.913</t>
+          <t>133976913461.732</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>129055.312</t>
+          <t>129055312073.648</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>126297.899</t>
+          <t>126297899404.134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6607.005</t>
+          <t>6607004824.3757</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6340.156</t>
+          <t>6340155720.54724</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6260.683</t>
+          <t>6260682678.37331</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6358.17</t>
+          <t>6358169648.4542</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6152.342</t>
+          <t>6152342270.75531</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6331.269</t>
+          <t>6331269191.62121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6460.406</t>
+          <t>6460406333.14541</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6495.704</t>
+          <t>6495703747.48512</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5875.606</t>
+          <t>5875606190.85604</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6294.394</t>
+          <t>6294393800.35261</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>6478.339</t>
+          <t>6478339300.30143</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6597.98</t>
+          <t>6597980038.4366</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6166.053</t>
+          <t>6166053389.6529</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>5845.069</t>
+          <t>5845069263.67446</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5299.247</t>
+          <t>5299246734.64305</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17384.236</t>
+          <t>17384236323.1763</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17531.604</t>
+          <t>17531604231.6626</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18350.874</t>
+          <t>18350873575.6226</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19583.932</t>
+          <t>19583932118.6227</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20627.26</t>
+          <t>20627259896.7261</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21773.954</t>
+          <t>21773954200.6877</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22085.252</t>
+          <t>22085251872.9986</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22039.418</t>
+          <t>22039417565.9789</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20099.463</t>
+          <t>20099462884.4259</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21413.432</t>
+          <t>21413432235.8866</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>21150.01</t>
+          <t>21150009814.0396</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>20968.975</t>
+          <t>20968975488.28</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20135.179</t>
+          <t>20135179052.9892</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>19416.091</t>
+          <t>19416090533.7419</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>19195.967</t>
+          <t>19195966534.3966</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>141196.888</t>
+          <t>141196887813.629</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>141672.796</t>
+          <t>141672796004.847</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>145679.827</t>
+          <t>145679827230.581</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>157986.923</t>
+          <t>157986922568.045</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>168664.16</t>
+          <t>168664159962.861</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>178787.094</t>
+          <t>178787093755.293</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>182633.497</t>
+          <t>182633496773.759</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>177824.268</t>
+          <t>177824268389.593</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>160977.038</t>
+          <t>160977037520.497</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>173173.376</t>
+          <t>173173376229.617</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>172766.989</t>
+          <t>172766988500.378</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>169972.742</t>
+          <t>169972742300.237</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>164872.022</t>
+          <t>164872022147.988</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>160935.295</t>
+          <t>160935294771.481</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>160438.503</t>
+          <t>160438503243.722</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>184899.765</t>
+          <t>184899764541.529</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>185244.07</t>
+          <t>185244069731.364</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>196732.174</t>
+          <t>196732174011.221</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>214973.301</t>
+          <t>214973301382.928</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>227204.062</t>
+          <t>227204061865.017</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>243194.685</t>
+          <t>243194684741.305</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>247000.216</t>
+          <t>247000215626.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>246680.507</t>
+          <t>246680507053.828</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>224341.189</t>
+          <t>224341188664.816</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>237510.595</t>
+          <t>237510595045.738</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>236562.784</t>
+          <t>236562783674.136</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>234425.933</t>
+          <t>234425933103.756</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>223144.566</t>
+          <t>223144566010.249</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>211839.392</t>
+          <t>211839392388.916</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>213704.99</t>
+          <t>213704990010.411</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>28195.771</t>
+          <t>28195770751.8978</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27776.483</t>
+          <t>27776483069.6658</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28013.455</t>
+          <t>28013455154.2599</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31674.577</t>
+          <t>31674576619.7559</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>33506.825</t>
+          <t>33506824855.4199</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>35395.259</t>
+          <t>35395258991.9036</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>35503.898</t>
+          <t>35503897876.3735</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>36581.574</t>
+          <t>36581573914.8896</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>34029.267</t>
+          <t>34029266676.0915</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>38092.772</t>
+          <t>38092772090.2696</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>37711.327</t>
+          <t>37711327244.6042</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>39870.37</t>
+          <t>39870370036.225</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>37758.284</t>
+          <t>37758284324.457</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>36215.518</t>
+          <t>36215518314.48</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>37378.041</t>
+          <t>37378041465.6046</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32820.993</t>
+          <t>32820993007.2358</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31905.281</t>
+          <t>31905281226.5442</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32348.874</t>
+          <t>32348873732.5378</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34709.494</t>
+          <t>34709493837.2896</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>38185.62</t>
+          <t>38185619618.1234</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>39252.791</t>
+          <t>39252791136.9375</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>38209.937</t>
+          <t>38209937127.5433</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>38021.451</t>
+          <t>38021451004.0762</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>34970.034</t>
+          <t>34970034160.6334</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>37429.238</t>
+          <t>37429237887.5365</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>36761.003</t>
+          <t>36761003485.2758</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>36184.954</t>
+          <t>36184953835.3922</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>33818.239</t>
+          <t>33818239270.8636</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>31782.389</t>
+          <t>31782388679.9251</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>31527.98</t>
+          <t>31527980000.1654</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>230988.958</t>
+          <t>230988958014.099</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>246848.325</t>
+          <t>246848324987.665</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>254618.441</t>
+          <t>254618441274.178</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>284731.438</t>
+          <t>284731438073.038</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>332532.772</t>
+          <t>332532772006.95</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>337758.381</t>
+          <t>337758381433.096</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>339186.983</t>
+          <t>339186983124.053</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>350994.754</t>
+          <t>350994754268.096</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>336259.911</t>
+          <t>336259911212.522</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>369281.363</t>
+          <t>369281362828.625</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>309972.299</t>
+          <t>309972299001.86</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>299736.937</t>
+          <t>299736937025.555</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>293645.756</t>
+          <t>293645756424.767</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>293100.794</t>
+          <t>293100793598.181</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>303608.304</t>
+          <t>303608303625.478</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1840434.938</t>
+          <t>1840434937820.31</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1890437.327</t>
+          <t>1890437327176.16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1944551.481</t>
+          <t>1944551480574.38</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2057041.707</t>
+          <t>2057041707282.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2107214.58</t>
+          <t>2107214579660.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2306190.438</t>
+          <t>2306190437574.09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2447800.054</t>
+          <t>2447800053530.15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2450733.572</t>
+          <t>2450733572443.73</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2458864.621</t>
+          <t>2458864621318.49</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2653450.849</t>
+          <t>2653450849054.25</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2666277.786</t>
+          <t>2666277786429.42</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2621100.453</t>
+          <t>2621100452690.32</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2460984.537</t>
+          <t>2460984537330.17</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2398092.978</t>
+          <t>2398092978282.19</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2428993.344</t>
+          <t>2428993344008.09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9875.415</t>
+          <t>9875415278.15528</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10501.047</t>
+          <t>10501047105.0054</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11079.438</t>
+          <t>11079438354.1063</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>12766.215</t>
+          <t>12766215377.3694</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13993.122</t>
+          <t>13993122455.7607</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15224.418</t>
+          <t>15224418151.1826</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15753.51</t>
+          <t>15753509512.4884</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16199.979</t>
+          <t>16199979473.9851</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15321.648</t>
+          <t>15321648188.8707</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>16846.157</t>
+          <t>16846156520.6355</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17518.377</t>
+          <t>17518377346.4205</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>18071.501</t>
+          <t>18071500654.0421</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>17683.938</t>
+          <t>17683937929.2827</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>17573.358</t>
+          <t>17573357837.4607</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>16715.937</t>
+          <t>16715937067.0172</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>108185.353</t>
+          <t>108185353449.596</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>110739.344</t>
+          <t>110739343699.469</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>114467.309</t>
+          <t>114467308848.313</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>125713.224</t>
+          <t>125713224229.252</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>133927.802</t>
+          <t>133927801515.787</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>143757.208</t>
+          <t>143757208070.303</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>143201.504</t>
+          <t>143201503967.95</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>144450.068</t>
+          <t>144450067891.142</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>137043.425</t>
+          <t>137043425438.402</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>144748.707</t>
+          <t>144748707253.924</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>146514.188</t>
+          <t>146514188186.439</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>147796.021</t>
+          <t>147796021087.578</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>143298.027</t>
+          <t>143298027102.454</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>140908.208</t>
+          <t>140908208084.251</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>138197.573</t>
+          <t>138197572945.673</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>564236.281</t>
+          <t>564236281258.321</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>562582.126</t>
+          <t>562582126077.215</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>569323.419</t>
+          <t>569323419185.915</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>596306.023</t>
+          <t>596306022650.903</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>602622.338</t>
+          <t>602622337720.212</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>636982.89</t>
+          <t>636982890210.875</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>639446.669</t>
+          <t>639446668675.442</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>620971.373</t>
+          <t>620971373147.59</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>569492.566</t>
+          <t>569492565544.409</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>601547.116</t>
+          <t>601547115847.066</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>581786.819</t>
+          <t>581786819495.459</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>571945.772</t>
+          <t>571945771910.645</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>534564.389</t>
+          <t>534564389231.507</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>494557.875</t>
+          <t>494557875479.782</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>458442.471</t>
+          <t>458442470671.43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>251108.183</t>
+          <t>251108183406.257</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>253890.08</t>
+          <t>253890079605.698</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>263522.482</t>
+          <t>263522481778.795</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>274390.211</t>
+          <t>274390211473.836</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>297847.779</t>
+          <t>297847779373.998</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>322556.082</t>
+          <t>322556082105.828</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>333493.01</t>
+          <t>333493010330.527</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>346362.763</t>
+          <t>346362762794.976</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>315419.929</t>
+          <t>315419928835.271</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>351074.663</t>
+          <t>351074662763.158</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>336243.677</t>
+          <t>336243677350.287</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>329096.439</t>
+          <t>329096438726.214</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>298837.958</t>
+          <t>298837958466.601</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>283921.007</t>
+          <t>283921006924.984</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>284951.234</t>
+          <t>284951234028.85</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12965.676</t>
+          <t>12965676214.0204</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12768.068</t>
+          <t>12768068286.2827</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12759.672</t>
+          <t>12759672127.6765</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13259.263</t>
+          <t>13259263234.8835</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12787.332</t>
+          <t>12787331881.9314</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13785.311</t>
+          <t>13785310567.6332</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13246.813</t>
+          <t>13246813407.9843</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13347.682</t>
+          <t>13347682307.2467</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12322.108</t>
+          <t>12322108225.1263</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13415.003</t>
+          <t>13415002964.2237</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>14197.707</t>
+          <t>14197707484.0046</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>14040.796</t>
+          <t>14040795548.325</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13844.509</t>
+          <t>13844509472.4032</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13690.562</t>
+          <t>13690562003.4442</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>12956.811</t>
+          <t>12956810780.6779</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1265.896</t>
+          <t>1265895689.14767</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1267.007</t>
+          <t>1267006672.76104</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1355.985</t>
+          <t>1355984752.39027</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1534.242</t>
+          <t>1534242368.14436</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1720.336</t>
+          <t>1720335859.98805</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1889.626</t>
+          <t>1889625795.35889</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1961.405</t>
+          <t>1961405313.18203</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1988.351</t>
+          <t>1988351176.04482</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1642.681</t>
+          <t>1642681460.7462</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2155.248</t>
+          <t>2155248360.4004</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2216.817</t>
+          <t>2216816954.42111</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2138.137</t>
+          <t>2138136595.35118</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2168.833</t>
+          <t>2168832669.72363</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2351.463</t>
+          <t>2351463189.73249</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2556.808</t>
+          <t>2556808356.7421</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7361.823</t>
+          <t>7361822919.958</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7180.598</t>
+          <t>7180597677.22013</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7158.005</t>
+          <t>7158004588.60686</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7637.306</t>
+          <t>7637306375.579</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7763.766</t>
+          <t>7763765531.21248</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7986.467</t>
+          <t>7986467056.85201</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7836.169</t>
+          <t>7836168758.09152</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7713.417</t>
+          <t>7713416853.22369</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6891.799</t>
+          <t>6891798957.05946</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7634.476</t>
+          <t>7634475704.3672</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7630.117</t>
+          <t>7630116805.10845</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7698.629</t>
+          <t>7698629466.50936</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7582.626</t>
+          <t>7582626325.51485</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7212.866</t>
+          <t>7212865632.12718</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6419.223</t>
+          <t>6419223176.5686</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>212652.542</t>
+          <t>212652541776.084</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>218254.177</t>
+          <t>218254177330.446</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>229377.29</t>
+          <t>229377290134.379</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>245909.154</t>
+          <t>245909154040.469</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>260624.867</t>
+          <t>260624866551.593</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>280313.13</t>
+          <t>280313130085.413</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>290238.128</t>
+          <t>290238128355.749</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>292517.186</t>
+          <t>292517185557.318</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>275362.649</t>
+          <t>275362649259.384</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>304346.612</t>
+          <t>304346611852.353</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>308055.842</t>
+          <t>308055842101.012</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>305184.854</t>
+          <t>305184853994.866</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>291789.108</t>
+          <t>291789107705.475</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>298598.979</t>
+          <t>298598978980.43</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>295226.947</t>
+          <t>295226946990.477</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>655.543</t>
+          <t>655542965.593269</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>653.812</t>
+          <t>653811703.128332</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>634.842</t>
+          <t>634842335.028257</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>643.603</t>
+          <t>643603285.946705</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>673.34</t>
+          <t>673340019.452608</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>707.08</t>
+          <t>707080205.418008</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>611.705</t>
+          <t>611705343.173336</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>717.138</t>
+          <t>717137963.024403</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>684.216</t>
+          <t>684215933.19612</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>771.824</t>
+          <t>771823890.570913</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>767.026</t>
+          <t>767026350.330811</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>775.998</t>
+          <t>775998440.007873</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>764.902</t>
+          <t>764901532.71713</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>773.192</t>
+          <t>773191519.531981</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>812.683</t>
+          <t>812683202.679585</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>41471.61</t>
+          <t>41471609686.1163</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>42661.448</t>
+          <t>42661448296.7081</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45167.3</t>
+          <t>45167299945.8002</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>48761.846</t>
+          <t>48761846476.5143</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>54427.168</t>
+          <t>54427168165.0895</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>52834.13</t>
+          <t>52834129753.5003</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>53178.13</t>
+          <t>53178129826.6568</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>53961.628</t>
+          <t>53961627654.0988</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>50807.918</t>
+          <t>50807917570.9628</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>54448.977</t>
+          <t>54448976963.4587</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>53854.588</t>
+          <t>53854588256.9436</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>53220.75</t>
+          <t>53220750242.6766</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>51172.578</t>
+          <t>51172578253.2589</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>49751.812</t>
+          <t>49751811695.8892</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>49798.218</t>
+          <t>49798218321.5249</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>107920.863</t>
+          <t>107920862996.413</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>107304.982</t>
+          <t>107304981705.742</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>111067.557</t>
+          <t>111067556806.485</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>119277.796</t>
+          <t>119277795501.661</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>121403.661</t>
+          <t>121403660603.328</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>121232.832</t>
+          <t>121232832395.071</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>116277.942</t>
+          <t>116277942021.289</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>112810.193</t>
+          <t>112810193103.123</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>104619.26</t>
+          <t>104619260307.417</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>114958.12</t>
+          <t>114958119748.146</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>115752.479</t>
+          <t>115752479092.378</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>117585.608</t>
+          <t>117585607566.088</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>115146.853</t>
+          <t>115146852550.454</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>113911.881</t>
+          <t>113911881433.305</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>116648.137</t>
+          <t>116648137294.425</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17399.354</t>
+          <t>17399353993.8658</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17389.587</t>
+          <t>17389587183.8321</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16924.856</t>
+          <t>16924855920.8246</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17178.705</t>
+          <t>17178704646.0769</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18208.045</t>
+          <t>18208045242.271</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>19258.743</t>
+          <t>19258743463.8272</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19690.593</t>
+          <t>19690593061.7748</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>19876.1</t>
+          <t>19876100485.082</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19287.185</t>
+          <t>19287185250.2051</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>21231.782</t>
+          <t>21231781820.4886</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21210.077</t>
+          <t>21210077301.7958</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22254.853</t>
+          <t>22254853334.9245</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>21667.399</t>
+          <t>21667398806.7204</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>21431.597</t>
+          <t>21431597235.4481</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>21586.947</t>
+          <t>21586947223.8636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>31293.178</t>
+          <t>31293178121.7161</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31832.222</t>
+          <t>31832221877.7479</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29293.971</t>
+          <t>29293971235.5034</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28896.677</t>
+          <t>28896676722.7606</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>34277.153</t>
+          <t>34277153472.0653</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>35111.261</t>
+          <t>35111260601.2959</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>34963.177</t>
+          <t>34963176935.4026</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>33925.249</t>
+          <t>33925249316.4317</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>33087.192</t>
+          <t>33087191792.047</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>35956.638</t>
+          <t>35956638491.748</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>35588.574</t>
+          <t>35588574379.0279</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>35961.72</t>
+          <t>35961720209.4407</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>35198.676</t>
+          <t>35198675620.5302</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>35033.81</t>
+          <t>35033809618.723</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>36006.606</t>
+          <t>36006605669.9484</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>600848.033</t>
+          <t>600848032951.605</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>581454.671</t>
+          <t>581454671158.324</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>575394.536</t>
+          <t>575394536316.224</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>587968.151</t>
+          <t>587968151291.057</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>606379.194</t>
+          <t>606379193698.521</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>638951.95</t>
+          <t>638951950352.549</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>650360.277</t>
+          <t>650360277317.857</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>648851.506</t>
+          <t>648851506246.042</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>597114.473</t>
+          <t>597114472965.914</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>638601.477</t>
+          <t>638601476869.193</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>628598.727</t>
+          <t>628598727425.933</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>615524.565</t>
+          <t>615524565064.372</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>583028.342</t>
+          <t>583028341695.551</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>557272.745</t>
+          <t>557272744820.623</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>544992.888</t>
+          <t>544992887562.261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16729.876</t>
+          <t>16729875916.311</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>16260.353</t>
+          <t>16260352827.8078</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16181.911</t>
+          <t>16181910877.6569</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>16751.6</t>
+          <t>16751600225.0007</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>16717.189</t>
+          <t>16717188585.9803</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17244.686</t>
+          <t>17244686499.7033</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17139.238</t>
+          <t>17139237828.5096</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16520.119</t>
+          <t>16520119474.4872</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14733.067</t>
+          <t>14733066768.4213</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>16140.246</t>
+          <t>16140246462.6528</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16590.646</t>
+          <t>16590646242.4085</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>16441.325</t>
+          <t>16441324788.685</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>15912.694</t>
+          <t>15912693815.2402</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>15713.621</t>
+          <t>15713620921.5615</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>15760.698</t>
+          <t>15760698372.7978</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6681.159</t>
+          <t>6681158881.18069</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6450.816</t>
+          <t>6450816379.6628</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6381.008</t>
+          <t>6381008211.5501</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6706.019</t>
+          <t>6706019246.85485</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7070.384</t>
+          <t>7070383546.11577</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7568.605</t>
+          <t>7568605276.67211</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7261.425</t>
+          <t>7261424789.98938</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>7421.468</t>
+          <t>7421467846.94648</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>7022.655</t>
+          <t>7022654553.1318</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>7518.884</t>
+          <t>7518883828.77021</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>7408.053</t>
+          <t>7408053210.26431</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>7484.301</t>
+          <t>7484301099.79327</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>7249.504</t>
+          <t>7249503930.97883</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>7209.688</t>
+          <t>7209687550.04027</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>7252.398</t>
+          <t>7252398315.46852</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>27961.771</t>
+          <t>27961771493.9766</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27586.769</t>
+          <t>27586768937.8806</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>27743.56</t>
+          <t>27743559797.6428</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29883.047</t>
+          <t>29883046602.2358</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>31763.839</t>
+          <t>31763838759.9828</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>35507.206</t>
+          <t>35507205772.5697</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>36288.716</t>
+          <t>36288716456.7426</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35325.358</t>
+          <t>35325357522.3444</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31756.473</t>
+          <t>31756473487.8127</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>34016.424</t>
+          <t>34016423991.763</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>33678.201</t>
+          <t>33678200679.3835</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>33736.9</t>
+          <t>33736899603.9072</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>32822.086</t>
+          <t>32822085797.4811</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>31682.203</t>
+          <t>31682202962.9493</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>30889.804</t>
+          <t>30889804297.1057</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>81803.194</t>
+          <t>81803194213.515</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>86042.72</t>
+          <t>86042720414.0239</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>89979.478</t>
+          <t>89979477557.6332</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>91480.022</t>
+          <t>91480021539.0758</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>95171.606</t>
+          <t>95171606041.2279</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>99585.182</t>
+          <t>99585182449.4626</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>100445.449</t>
+          <t>100445449308.642</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>102861.164</t>
+          <t>102861164430.468</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>98934.344</t>
+          <t>98934343649.3486</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>101116.367</t>
+          <t>101116367270.723</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>107414.621</t>
+          <t>107414620611.749</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>104690.92</t>
+          <t>104690920194.777</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>100507.097</t>
+          <t>100507097250.345</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>99625.405</t>
+          <t>99625404864.5153</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>101458.173</t>
+          <t>101458172604.787</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>75138.757</t>
+          <t>75138757321.3962</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>74643.77</t>
+          <t>74643769918.7581</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>77438.731</t>
+          <t>77438731415.9219</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>82336.285</t>
+          <t>82336285436.533</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>86268.009</t>
+          <t>86268008951.5921</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>92637.299</t>
+          <t>92637298797.2919</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>89082.079</t>
+          <t>89082079266.7009</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>89979.626</t>
+          <t>89979626464.6979</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>84371.384</t>
+          <t>84371383827.3622</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>92032.746</t>
+          <t>92032746482.1866</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>93288.316</t>
+          <t>93288316304.6141</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>94403.508</t>
+          <t>94403507805.7132</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>91681.247</t>
+          <t>91681246508.3571</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>90781.72</t>
+          <t>90781720360.2616</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>91809.442</t>
+          <t>91809442272.1275</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1183902.64</t>
+          <t>1183902639540.63</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1187538.851</t>
+          <t>1187538850544.23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1225155.377</t>
+          <t>1225155377391.07</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1336354.541</t>
+          <t>1336354541162.71</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1393177.115</t>
+          <t>1393177115218.2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1486651.28</t>
+          <t>1486651280225.51</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1466218.745</t>
+          <t>1466218744744.71</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1421319.621</t>
+          <t>1421319621062.31</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1285643.118</t>
+          <t>1285643118435.57</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1376838.635</t>
+          <t>1376838634824.57</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1359844.555</t>
+          <t>1359844555309.35</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1356344.44</t>
+          <t>1356344440147.41</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1282520.899</t>
+          <t>1282520899069.87</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1211604.647</t>
+          <t>1211604647235.39</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1173613.427</t>
+          <t>1173613426572.88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4576275.274</t>
+          <t>4576275273914.6</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4717824.378</t>
+          <t>4717824378082.3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4873185.831</t>
+          <t>4873185830699</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5145858.817</t>
+          <t>5145858817495.55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>5352766.317</t>
+          <t>5352766317473.25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5838362.502</t>
+          <t>5838362502346.44</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6175306.454</t>
+          <t>6175306454123.01</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6250794.418</t>
+          <t>6250794418383.24</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6099766.238</t>
+          <t>6099766238239</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>6849742.933</t>
+          <t>6849742933147.94</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>6894884.969</t>
+          <t>6894884969049.5</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6981204.377</t>
+          <t>6981204377116.96</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6860902.913</t>
+          <t>6860902912758.31</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>6934098.229</t>
+          <t>6934098228999.89</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7203996.413</t>
+          <t>7203996412995.46</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13896755.55</t>
+          <t>13896755550416.6</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14137242.534</t>
+          <t>14137242533657.8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14536648.668</t>
+          <t>14536648668415.7</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15397464.104</t>
+          <t>15397464104296.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16008155.112</t>
+          <t>16008155111814.9</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17226215.879</t>
+          <t>17226215879060.7</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18024202.075</t>
+          <t>18024202075487.7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>18236395.009</t>
+          <t>18236395009250.4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17519868.245</t>
+          <t>17519868245095.8</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>19142797.433</t>
+          <t>19142797433490.9</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19145372.628</t>
+          <t>19145372627895.9</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>19091627.608</t>
+          <t>19091627607836.3</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>18406779.856</t>
+          <t>18406779855955.8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>18246591.442</t>
+          <t>18246591442303.1</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>18569964.468</t>
+          <t>18569964467628.7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
